--- a/database_penyimpanan_aman/database_master_po.xlsx
+++ b/database_penyimpanan_aman/database_master_po.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,15 +1716,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4500011236</t>
-        </is>
+      <c r="A38" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4500011236</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1753,6 +1749,84 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4500011586</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4500011580</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_master_po.xlsx
+++ b/database_penyimpanan_aman/database_master_po.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18300</v>
+        <v>4600</v>
       </c>
       <c r="G17" t="n">
-        <v>65000</v>
+        <v>25000</v>
       </c>
       <c r="H17" t="n">
-        <v>1189500000</v>
+        <v>115000000</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -1000,27 +1000,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9200</v>
+        <v>150</v>
       </c>
       <c r="G18" t="n">
-        <v>33000</v>
+        <v>500000</v>
       </c>
       <c r="H18" t="n">
-        <v>303600000</v>
+        <v>75000000</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -1033,27 +1033,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4600</v>
+        <v>480</v>
       </c>
       <c r="G19" t="n">
-        <v>25000</v>
+        <v>500000</v>
       </c>
       <c r="H19" t="n">
-        <v>115000000</v>
+        <v>240000000</v>
       </c>
       <c r="I19" t="inlineStr"/>
     </row>
@@ -1062,101 +1062,109 @@
         <v>7201250141</v>
       </c>
       <c r="B20" t="n">
-        <v>4500011739</v>
+        <v>4500011794</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>500000</v>
+        <v>11500</v>
       </c>
       <c r="H20" t="n">
-        <v>75000000</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>575000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>7201250141</v>
       </c>
       <c r="B21" t="n">
-        <v>4500011739</v>
+        <v>4500011794</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>500000</v>
+        <v>17250</v>
       </c>
       <c r="H21" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>862500</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>7201250141</v>
       </c>
       <c r="B22" t="n">
-        <v>4500011794</v>
+        <v>4500011581</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>SAFETY EQUIPMENT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Barricade Tape/ police line 3" panjang @300m</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>11500</v>
+        <v>250000</v>
       </c>
       <c r="H22" t="n">
-        <v>575000</v>
+        <v>1000000</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1165,35 +1173,35 @@
         <v>7201250141</v>
       </c>
       <c r="B23" t="n">
-        <v>4500011794</v>
+        <v>4500011581</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>0.4</v>
       </c>
       <c r="G23" t="n">
-        <v>17250</v>
+        <v>712500</v>
       </c>
       <c r="H23" t="n">
-        <v>862500</v>
+        <v>285000</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1202,16 +1210,16 @@
         <v>7201250141</v>
       </c>
       <c r="B24" t="n">
-        <v>4500011581</v>
+        <v>4500011203</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAFETY EQUIPMENT</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Barricade Tape/ police line 3" panjang @300m</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1220,13 +1228,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>0.524</v>
       </c>
       <c r="G24" t="n">
-        <v>250000</v>
+        <v>3125000</v>
       </c>
       <c r="H24" t="n">
-        <v>1000000</v>
+        <v>1637500</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1239,7 +1247,7 @@
         <v>7201250141</v>
       </c>
       <c r="B25" t="n">
-        <v>4500011581</v>
+        <v>4500011203</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1257,13 +1265,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>712500</v>
+        <v>55500</v>
       </c>
       <c r="H25" t="n">
-        <v>285000</v>
+        <v>55500</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1285,7 +1293,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1294,13 +1302,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.524</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3125000</v>
+        <v>75000</v>
       </c>
       <c r="H26" t="n">
-        <v>1637500</v>
+        <v>75000</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1322,7 +1330,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1334,10 +1342,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>55500</v>
+        <v>293750</v>
       </c>
       <c r="H27" t="n">
-        <v>55500</v>
+        <v>293750</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1359,7 +1367,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1371,10 +1379,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>75000</v>
+        <v>400000</v>
       </c>
       <c r="H28" t="n">
-        <v>75000</v>
+        <v>400000</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1396,7 +1404,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1405,13 +1413,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>293750</v>
+        <v>120000</v>
       </c>
       <c r="H29" t="n">
-        <v>293750</v>
+        <v>1440000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1433,7 +1441,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1442,13 +1450,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>400000</v>
+        <v>93750</v>
       </c>
       <c r="H30" t="n">
-        <v>400000</v>
+        <v>187500</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1470,7 +1478,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1479,13 +1487,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>120000</v>
+        <v>37500</v>
       </c>
       <c r="H31" t="n">
-        <v>1440000</v>
+        <v>75000</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1507,7 +1515,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1516,13 +1524,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>93750</v>
+        <v>37500</v>
       </c>
       <c r="H32" t="n">
-        <v>187500</v>
+        <v>37500</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1544,7 +1552,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1553,13 +1561,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="G33" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="H33" t="n">
-        <v>75000</v>
+        <v>2125000</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1581,7 +1589,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1590,13 +1598,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G34" t="n">
-        <v>37500</v>
+        <v>712500</v>
       </c>
       <c r="H34" t="n">
-        <v>37500</v>
+        <v>142500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1618,7 +1626,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1627,13 +1635,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>31250</v>
+        <v>50000</v>
       </c>
       <c r="H35" t="n">
-        <v>2125000</v>
+        <v>450000</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1646,35 +1654,35 @@
         <v>7201250141</v>
       </c>
       <c r="B36" t="n">
-        <v>4500011203</v>
+        <v>4500011236</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>712500</v>
+        <v>890007884.9999999</v>
       </c>
       <c r="H36" t="n">
-        <v>142500</v>
+        <v>890007884.9999999</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
     </row>
@@ -1683,35 +1691,35 @@
         <v>7201250141</v>
       </c>
       <c r="B37" t="n">
-        <v>4500011203</v>
+        <v>4500011586</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>50000</v>
+        <v>24150000</v>
       </c>
       <c r="H37" t="n">
-        <v>450000</v>
+        <v>24150000</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
     </row>
@@ -1720,35 +1728,35 @@
         <v>7201250141</v>
       </c>
       <c r="B38" t="n">
-        <v>4500011236</v>
+        <v>4500011580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>890007884.9999999</v>
+        <v>1600000</v>
       </c>
       <c r="H38" t="n">
-        <v>890007884.9999999</v>
+        <v>1600000</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1757,16 +1765,16 @@
         <v>7201250141</v>
       </c>
       <c r="B39" t="n">
-        <v>4500011586</v>
+        <v>4500011739</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1775,17 +1783,17 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>18300</v>
       </c>
       <c r="G39" t="n">
-        <v>24150000</v>
+        <v>65000</v>
       </c>
       <c r="H39" t="n">
-        <v>24150000</v>
+        <v>1189500000</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1805,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4500011580</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>9200</v>
       </c>
       <c r="G40" t="n">
-        <v>1600000</v>
+        <v>33000</v>
       </c>
       <c r="H40" t="n">
-        <v>1600000</v>
+        <v>303600000</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>

--- a/database_penyimpanan_aman/database_master_po.xlsx
+++ b/database_penyimpanan_aman/database_master_po.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,15 +1798,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="A40" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4500011739</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1835,6 +1831,47 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>45000test</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>50</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11500</v>
+      </c>
+      <c r="H41" t="n">
+        <v>575000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Garam Kasar</t>
         </is>
       </c>
     </row>
